--- a/data/controles_results/difmedias_controles_staggered_variables_2019.xlsx
+++ b/data/controles_results/difmedias_controles_staggered_variables_2019.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="126" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="126" uniqueCount="56">
   <si>
     <t/>
   </si>
@@ -48,7 +48,7 @@
     <t>N</t>
   </si>
   <si>
-    <t>835</t>
+    <t>832</t>
   </si>
   <si>
     <t xml:space="preserve"> (1) </t>
@@ -60,25 +60,25 @@
     <t>Mean/(SE)</t>
   </si>
   <si>
-    <t>0.068</t>
+    <t>0.069</t>
   </si>
   <si>
     <t>(0.009)</t>
   </si>
   <si>
-    <t>0.158</t>
+    <t>0.157</t>
   </si>
   <si>
     <t>(0.013)</t>
   </si>
   <si>
-    <t>0.074</t>
+    <t>0.073</t>
   </si>
   <si>
     <t>0.144</t>
   </si>
   <si>
-    <t>(0.031)</t>
+    <t>(0.032)</t>
   </si>
   <si>
     <t>0.202</t>
@@ -87,19 +87,19 @@
     <t>(0.019)</t>
   </si>
   <si>
-    <t>0.089</t>
+    <t>0.088</t>
   </si>
   <si>
     <t>(0.012)</t>
   </si>
   <si>
-    <t>2.792</t>
-  </si>
-  <si>
-    <t>(0.052)</t>
-  </si>
-  <si>
-    <t>61</t>
+    <t>2.789</t>
+  </si>
+  <si>
+    <t>(0.053)</t>
+  </si>
+  <si>
+    <t>64</t>
   </si>
   <si>
     <t xml:space="preserve"> (2) </t>
@@ -108,43 +108,46 @@
     <t>1</t>
   </si>
   <si>
-    <t>0.082</t>
-  </si>
-  <si>
-    <t>(0.035)</t>
-  </si>
-  <si>
-    <t>0.393</t>
-  </si>
-  <si>
-    <t>(0.063)</t>
-  </si>
-  <si>
-    <t>0.148</t>
+    <t>0.078</t>
+  </si>
+  <si>
+    <t>(0.034)</t>
+  </si>
+  <si>
+    <t>0.391</t>
+  </si>
+  <si>
+    <t>(0.061)</t>
+  </si>
+  <si>
+    <t>0.156</t>
   </si>
   <si>
     <t>(0.046)</t>
   </si>
   <si>
-    <t>0.197</t>
-  </si>
-  <si>
-    <t>(0.112)</t>
-  </si>
-  <si>
-    <t>0.508</t>
-  </si>
-  <si>
-    <t>(0.089)</t>
-  </si>
-  <si>
-    <t>(0.069)</t>
-  </si>
-  <si>
-    <t>3.660</t>
-  </si>
-  <si>
-    <t>(0.092)</t>
+    <t>0.188</t>
+  </si>
+  <si>
+    <t>(0.107)</t>
+  </si>
+  <si>
+    <t>0.500</t>
+  </si>
+  <si>
+    <t>(0.086)</t>
+  </si>
+  <si>
+    <t>0.203</t>
+  </si>
+  <si>
+    <t>(0.067)</t>
+  </si>
+  <si>
+    <t>3.656</t>
+  </si>
+  <si>
+    <t>(0.088)</t>
   </si>
   <si>
     <t>896</t>
@@ -159,22 +162,22 @@
     <t>Mean difference</t>
   </si>
   <si>
-    <t>0.014</t>
-  </si>
-  <si>
-    <t>0.235***</t>
-  </si>
-  <si>
-    <t>0.073**</t>
-  </si>
-  <si>
-    <t>0.053</t>
-  </si>
-  <si>
-    <t>0.306***</t>
-  </si>
-  <si>
-    <t>0.108**</t>
+    <t>0.010</t>
+  </si>
+  <si>
+    <t>0.233***</t>
+  </si>
+  <si>
+    <t>0.083**</t>
+  </si>
+  <si>
+    <t>0.043</t>
+  </si>
+  <si>
+    <t>0.298***</t>
+  </si>
+  <si>
+    <t>0.115**</t>
   </si>
   <si>
     <t>0.868***</t>
@@ -244,7 +247,7 @@
         <v>0</v>
       </c>
       <c r="G1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="2">
@@ -267,7 +270,7 @@
         <v>0</v>
       </c>
       <c r="G2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="3">
@@ -290,7 +293,7 @@
         <v>10</v>
       </c>
       <c r="G3" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="4">
@@ -310,10 +313,10 @@
         <v>31</v>
       </c>
       <c r="F4" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="G4" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="5">
@@ -356,10 +359,10 @@
         <v>33</v>
       </c>
       <c r="F6" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="G6" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="7">
@@ -402,10 +405,10 @@
         <v>35</v>
       </c>
       <c r="F8" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="G8" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="9">
@@ -448,10 +451,10 @@
         <v>37</v>
       </c>
       <c r="F10" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="G10" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="11">
@@ -494,10 +497,10 @@
         <v>39</v>
       </c>
       <c r="F12" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="G12" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="13">
@@ -537,13 +540,13 @@
         <v>28</v>
       </c>
       <c r="E14" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="F14" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="G14" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="15">
@@ -560,7 +563,7 @@
         <v>0</v>
       </c>
       <c r="E15" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F15" t="s">
         <v>0</v>
@@ -583,13 +586,13 @@
         <v>28</v>
       </c>
       <c r="E16" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F16" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="G16" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="17">
@@ -606,7 +609,7 @@
         <v>0</v>
       </c>
       <c r="E17" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F17" t="s">
         <v>0</v>
